--- a/results/Int Task Remove ACC -0.4/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.4/Linea_fi_all.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.00046282011724773086 +/- 0.0010348972435204253</t>
+          <t>0.0004936747917309136 +/- 0.0010435997855777737</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.036051373954599696 +/- 0.0035367474195258284</t>
+          <t>-0.035991636798088346 +/- 0.003522086739611734</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.010752688172043057 +/- 0.003250052690259369</t>
+          <t>0.010782556750298733 +/- 0.0032237315774986943</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0007973014412757217 +/- 0.0010189051043137855</t>
+          <t>0.0007359705611775901 +/- 0.000981294081570073</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.00012266176019621878 +/- 0.0003679852805887581</t>
+          <t>-0.00015332720024527902 +/- 0.00031422725439923853</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.0014547754585704897 +/- 0.0008626300883609003</t>
+          <t>-0.0015180265654648694 +/- 0.0007975661108740245</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.13972169512966479 +/- 0.005398251307615892</t>
+          <t>0.1396900695762176 +/- 0.005376437101550538</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.11514864010120181 +/- 0.005684599762237844</t>
+          <t>0.11511701454775465 +/- 0.005676764820361132</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.015524827152734112 +/- 0.004042221292473534</t>
+          <t>-0.015524827152734112 +/- 0.003955781012585681</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0003142677561282503 +/- 0.0016208418552140272</t>
+          <t>0.00028284098051541975 +/- 0.0016417294640614687</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.002545568824638622 +/- 0.001110659776685886</t>
+          <t>0.002545568824638622 +/- 0.0011283044042122183</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.002639849151477092 +/- 0.002507061052819493</t>
+          <t>0.0026398491514771027 +/- 0.0024472561073452886</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.004236006051437191 +/- 0.00349467224640989</t>
+          <t>0.004296520423600581 +/- 0.0035872315486302903</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.00039334341906203105 +/- 0.00042896964837391724</t>
+          <t>-0.0003630862329803364 +/- 0.0004841149773071151</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.004774110861903202 +/- 0.0037019504190531315</t>
+          <t>0.004774110861903202 +/- 0.0038058734912332264</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.01256007689842994 +/- 0.003304421168690478</t>
+          <t>0.01252803588593394 +/- 0.0033618642057330977</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.004549823774431217 +/- 0.0017002882616368627</t>
+          <t>0.004517782761935219 +/- 0.0016799393436614325</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
